--- a/data/file_generation/reference/data_107/A店_揽收明细_res.xlsx
+++ b/data/file_generation/reference/data_107/A店_揽收明细_res.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0206/data_107/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/output/data_107/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA0C36D-9723-C547-9073-F3AC525644F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA17965-1C0B-2941-A558-8EF35033F526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="500" windowWidth="34760" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="揽收明细" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>运单编号</t>
   </si>
@@ -62,7 +65,7 @@
     <t>客户D</t>
   </si>
   <si>
-    <t>2025-10-03 15:46:57</t>
+    <t>2025年10月</t>
   </si>
   <si>
     <t>湖南省</t>
@@ -77,43 +80,28 @@
     <t>36BBDSRSZWDQ</t>
   </si>
   <si>
-    <t>2025-10-03 18:40:41</t>
-  </si>
-  <si>
     <t>广东省</t>
   </si>
   <si>
     <t>CVU5QBDVE8OX</t>
   </si>
   <si>
-    <t>2025-10-03 18:40:43</t>
-  </si>
-  <si>
     <t>江苏省</t>
   </si>
   <si>
     <t>JG5BM3E59L4K</t>
   </si>
   <si>
-    <t>2025-10-01 17:53:56</t>
-  </si>
-  <si>
     <t>内蒙古自治区</t>
   </si>
   <si>
     <t>6HW26N3KGYV5</t>
   </si>
   <si>
-    <t>2025-10-03 15:47:05</t>
-  </si>
-  <si>
     <t>甘肃省</t>
   </si>
   <si>
     <t>VXNWVI8VTM58</t>
-  </si>
-  <si>
-    <t>2025-10-05 19:42:41</t>
   </si>
   <si>
     <t>四川省</t>
@@ -481,7 +469,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.1"/>
   <cols>
     <col min="1" max="8" width="15" customWidth="1"/>
   </cols>
@@ -547,10 +535,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
       </c>
       <c r="E3">
         <v>0.33</v>
@@ -561,16 +549,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>0.33</v>
@@ -581,16 +569,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>0.2</v>
@@ -601,16 +589,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>1.0900000000000001</v>
@@ -621,16 +609,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>1.1000000000000001</v>
@@ -646,6 +634,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -793,29 +796,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5100DAF8-8EF6-4661-AEE9-FFE644DF2565}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6688BDCC-B0F1-4263-9179-6C6C733A8F6E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B38028A-733C-453D-8214-ECD329AFC215}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EE4E79B-B97F-445C-81A5-F6708892AA31}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BACCCC96-6957-4ADC-8901-60F6AD7018AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FED35BE-725C-4633-8D67-7C647C955C44}"/>
 </file>